--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción cobalto 2018 y 2019.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción cobalto 2018 y 2019.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,20 +456,25 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Velocidad [km/s]</t>
+          <t>Velocidad obs. [km/s]</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Velocidad heliocéntrica [km/s]</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Profundidad / Altura</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>FWHM [Å]</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>EW [Å]</t>
         </is>
@@ -501,13 +506,16 @@
         <v>19.71</v>
       </c>
       <c r="G2" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.5629</v>
       </c>
-      <c r="H2" t="n">
-        <v>0.9429999999999999</v>
-      </c>
       <c r="I2" t="n">
-        <v>0.6163</v>
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6153999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -536,13 +544,16 @@
         <v>19.4</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5504</v>
+        <v>-4.47</v>
       </c>
       <c r="H3" t="n">
-        <v>0.959</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6089</v>
+        <v>0.963</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6576</v>
       </c>
     </row>
     <row r="4">
@@ -571,13 +582,16 @@
         <v>23.47</v>
       </c>
       <c r="G4" t="n">
+        <v>-2.53</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.5656</v>
       </c>
-      <c r="H4" t="n">
-        <v>0.929</v>
-      </c>
       <c r="I4" t="n">
-        <v>0.6011</v>
+        <v>0.928</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6006</v>
       </c>
     </row>
     <row r="5">
@@ -606,13 +620,16 @@
         <v>24.06</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5551</v>
+        <v>-2.53</v>
       </c>
       <c r="H5" t="n">
-        <v>0.89</v>
+        <v>0.5595</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.846</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.536</v>
       </c>
     </row>
     <row r="6">
@@ -641,13 +658,16 @@
         <v>24.2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5483</v>
+        <v>-3.38</v>
       </c>
       <c r="H6" t="n">
-        <v>0.913</v>
+        <v>0.5556</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6128</v>
+        <v>0.873</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5994</v>
       </c>
     </row>
     <row r="7">
@@ -676,13 +696,16 @@
         <v>25.74</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5524</v>
+        <v>-2.45</v>
       </c>
       <c r="H7" t="n">
-        <v>0.848</v>
+        <v>0.5563</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5523</v>
+        <v>0.824</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5276</v>
       </c>
     </row>
     <row r="8">
@@ -711,12 +734,15 @@
         <v>26.07</v>
       </c>
       <c r="G8" t="n">
+        <v>-3.14</v>
+      </c>
+      <c r="H8" t="n">
         <v>0.5606</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>0.896</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>0.6126</v>
       </c>
     </row>
@@ -746,13 +772,16 @@
         <v>26.94</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5601</v>
+        <v>-2.53</v>
       </c>
       <c r="H9" t="n">
-        <v>0.875</v>
+        <v>0.5613</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.862</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5947</v>
       </c>
     </row>
     <row r="10">
@@ -781,13 +810,16 @@
         <v>26.66</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5605</v>
+        <v>-2.7</v>
       </c>
       <c r="H10" t="n">
-        <v>0.967</v>
+        <v>0.5615</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6563</v>
+        <v>0.961</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6451</v>
       </c>
     </row>
     <row r="11">
@@ -816,13 +848,16 @@
         <v>22.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5322</v>
+        <v>-3.74</v>
       </c>
       <c r="H11" t="n">
-        <v>0.961</v>
+        <v>0.5371</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6093</v>
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5981</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción cobalto 2018 y 2019.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción cobalto 2018 y 2019.xlsx
@@ -499,8 +499,10 @@
       <c r="D2" t="n">
         <v>6563.829</v>
       </c>
-      <c r="E2" t="n">
-        <v>6.600000000000001e-05</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6.6e-05</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>19.71</v>
@@ -509,13 +511,13 @@
         <v>-3.12</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5629</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="3">
@@ -537,8 +539,10 @@
       <c r="D3" t="n">
         <v>6563.822</v>
       </c>
-      <c r="E3" t="n">
-        <v>6.499999999999999e-05</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6.5e-05</t>
+        </is>
       </c>
       <c r="F3" t="n">
         <v>19.4</v>
@@ -547,13 +551,13 @@
         <v>-4.47</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.963</v>
+        <v>0.96</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6576</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="4">
@@ -575,8 +579,10 @@
       <c r="D4" t="n">
         <v>6563.911</v>
       </c>
-      <c r="E4" t="n">
-        <v>7.8e-05</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7.8e-05</t>
+        </is>
       </c>
       <c r="F4" t="n">
         <v>23.47</v>
@@ -585,13 +591,13 @@
         <v>-2.53</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5656</v>
+        <v>0.57</v>
       </c>
       <c r="I4" t="n">
-        <v>0.928</v>
+        <v>0.93</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6006</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
@@ -613,8 +619,10 @@
       <c r="D5" t="n">
         <v>6563.924</v>
       </c>
-      <c r="E5" t="n">
-        <v>8.000000000000001e-05</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8e-05</t>
+        </is>
       </c>
       <c r="F5" t="n">
         <v>24.06</v>
@@ -623,13 +631,13 @@
         <v>-2.53</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5595</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.846</v>
+        <v>0.85</v>
       </c>
       <c r="J5" t="n">
-        <v>0.536</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="6">
@@ -651,8 +659,10 @@
       <c r="D6" t="n">
         <v>6563.927</v>
       </c>
-      <c r="E6" t="n">
-        <v>8.1e-05</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8.1e-05</t>
+        </is>
       </c>
       <c r="F6" t="n">
         <v>24.2</v>
@@ -661,13 +671,13 @@
         <v>-3.38</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5556</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.873</v>
+        <v>0.87</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5994</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7">
@@ -689,8 +699,10 @@
       <c r="D7" t="n">
         <v>6563.961</v>
       </c>
-      <c r="E7" t="n">
-        <v>8.6e-05</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8.6e-05</t>
+        </is>
       </c>
       <c r="F7" t="n">
         <v>25.74</v>
@@ -699,13 +711,13 @@
         <v>-2.45</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5563</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.824</v>
+        <v>0.82</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5276</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="8">
@@ -727,8 +739,10 @@
       <c r="D8" t="n">
         <v>6563.968</v>
       </c>
-      <c r="E8" t="n">
-        <v>8.7e-05</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8.7e-05</t>
+        </is>
       </c>
       <c r="F8" t="n">
         <v>26.07</v>
@@ -737,13 +751,13 @@
         <v>-3.14</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5606</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.896</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6126</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="9">
@@ -765,8 +779,10 @@
       <c r="D9" t="n">
         <v>6563.987</v>
       </c>
-      <c r="E9" t="n">
-        <v>9.000000000000001e-05</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>9e-05</t>
+        </is>
       </c>
       <c r="F9" t="n">
         <v>26.94</v>
@@ -775,13 +791,13 @@
         <v>-2.53</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5613</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.862</v>
+        <v>0.86</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5947</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="10">
@@ -803,8 +819,10 @@
       <c r="D10" t="n">
         <v>6563.981</v>
       </c>
-      <c r="E10" t="n">
-        <v>8.899999999999999e-05</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8.9e-05</t>
+        </is>
       </c>
       <c r="F10" t="n">
         <v>26.66</v>
@@ -813,13 +831,13 @@
         <v>-2.7</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5615</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.961</v>
+        <v>0.96</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6451</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="11">
@@ -841,8 +859,10 @@
       <c r="D11" t="n">
         <v>6563.89</v>
       </c>
-      <c r="E11" t="n">
-        <v>7.499999999999999e-05</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>7.5e-05</t>
+        </is>
       </c>
       <c r="F11" t="n">
         <v>22.5</v>
@@ -851,13 +871,13 @@
         <v>-3.74</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5371</v>
+        <v>0.54</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5981</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción cobalto 2018 y 2019.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción cobalto 2018 y 2019.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,41 +843,121 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Septiembre 21-2018</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hα</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Absorción Cobalto</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6563.927</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8.1e-05</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Agosto 05-2019</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Hα</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Absorción Cobalto</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Absorción Cobalto</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>6563.89</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>7.5e-05</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F12" t="n">
         <v>22.5</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G12" t="n">
         <v>-3.74</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H12" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Agosto 06-2019</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Hα</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Absorción Cobalto</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6563.907</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>7.8e-05</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-3.13</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J13" t="n">
         <v>0.54</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.6</v>
       </c>
     </row>
   </sheetData>
